--- a/data/trans_orig/P36BPD06_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023</t>
+          <t>Población según el número de raciones de mantequilla, margarina o nata que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27321</t>
+          <t>28151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>33672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55996</t>
+          <t>57901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277658</t>
+          <t>276365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296885</t>
+          <t>297097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262314</t>
+          <t>261484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>274275</t>
+          <t>273685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545081</t>
+          <t>543176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567665</t>
+          <t>567405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63907</t>
+          <t>63997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112625</t>
+          <t>110417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102507</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135102</t>
+          <t>136421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176707</t>
+          <t>178194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236623</t>
+          <t>232751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404489</t>
+          <t>406697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>453207</t>
+          <t>453117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>379867</t>
+          <t>378548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>412462</t>
+          <t>413574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>795460</t>
+          <t>799332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855376</t>
+          <t>853889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54858</t>
+          <t>55788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83743</t>
+          <t>84030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281207</t>
+          <t>281696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300102</t>
+          <t>299801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286600</t>
+          <t>287242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308809</t>
+          <t>309976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576514</t>
+          <t>576227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605399</t>
+          <t>604469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31227</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61872</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49202</t>
+          <t>46825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259253</t>
+          <t>242851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>94250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345419</t>
+          <t>335024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249118</t>
+          <t>248972</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279763</t>
+          <t>278739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216064</t>
+          <t>232466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>426115</t>
+          <t>428492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>440888</t>
+          <t>451283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694514</t>
+          <t>692057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46646</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>53381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78863</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130734</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149875</t>
+          <t>149902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171904</t>
+          <t>171545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186347</t>
+          <t>186285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306378</t>
+          <t>307926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331743</t>
+          <t>331860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>25019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41020</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250207</t>
+          <t>248832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262465</t>
+          <t>262049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231602</t>
+          <t>232037</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245369</t>
+          <t>245865</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485281</t>
+          <t>486160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504306</t>
+          <t>504534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>87426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139181</t>
+          <t>139202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134760</t>
+          <t>136015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>626232</t>
+          <t>580883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240800</t>
+          <t>238737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>749384</t>
+          <t>795938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>479507</t>
+          <t>479486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>531903</t>
+          <t>531262</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222220</t>
+          <t>267569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>713692</t>
+          <t>712437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>717755</t>
+          <t>671201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1226339</t>
+          <t>1228402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>186722</t>
+          <t>182453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>562813</t>
+          <t>564222</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>380764</t>
+          <t>382277</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>428571</t>
+          <t>427553</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>504438</t>
+          <t>506725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>969138</t>
+          <t>972250</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>363503</t>
+          <t>362094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>739594</t>
+          <t>743863</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>289160</t>
+          <t>290178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336967</t>
+          <t>335454</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>674910</t>
+          <t>671798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1139610</t>
+          <t>1137323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>580597</t>
+          <t>582424</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>824014</t>
+          <t>821203</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>879135</t>
+          <t>866545</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1570904</t>
+          <t>1559226</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1562250</t>
+          <t>1589899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2291013</t>
+          <t>2362623</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2621376</t>
+          <t>2624187</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2864793</t>
+          <t>2862966</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2086159</t>
+          <t>2097837</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2777928</t>
+          <t>2790518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4811440</t>
+          <t>4739830</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5540203</t>
+          <t>5512554</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD06_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD06_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>36056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33672</t>
+          <t>41628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57901</t>
+          <t>65793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>288972</t>
+          <t>293239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276365</t>
+          <t>282789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297097</t>
+          <t>301559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>268310</t>
+          <t>289434</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261484</t>
+          <t>281308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273685</t>
+          <t>296656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557281</t>
+          <t>582674</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543176</t>
+          <t>569113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567405</t>
+          <t>593278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86089</t>
+          <t>89671</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63997</t>
+          <t>69916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110417</t>
+          <t>117053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>118341</t>
+          <t>126600</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101395</t>
+          <t>109170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136421</t>
+          <t>148477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>204431</t>
+          <t>216271</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178194</t>
+          <t>190211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232751</t>
+          <t>248663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>431025</t>
+          <t>439690</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406697</t>
+          <t>412308</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>453117</t>
+          <t>459445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>396628</t>
+          <t>419894</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>378548</t>
+          <t>398017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>413574</t>
+          <t>437324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>827652</t>
+          <t>859584</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>799332</t>
+          <t>827192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>853889</t>
+          <t>885644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517114</t>
+          <t>529361</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032083</t>
+          <t>1075855</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032083</t>
+          <t>1075855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032083</t>
+          <t>1075855</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>34783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46637</t>
+          <t>50379</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>39911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>62819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68529</t>
+          <t>73892</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55788</t>
+          <t>60683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84030</t>
+          <t>90371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>292322</t>
+          <t>290691</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281696</t>
+          <t>279421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299801</t>
+          <t>298580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>299406</t>
+          <t>302359</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287242</t>
+          <t>289919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309976</t>
+          <t>312827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>591728</t>
+          <t>593051</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>576227</t>
+          <t>576572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>604469</t>
+          <t>606260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314214</t>
+          <t>314204</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314214</t>
+          <t>314204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314214</t>
+          <t>314204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>346043</t>
+          <t>352738</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>346043</t>
+          <t>352738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>346043</t>
+          <t>352738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>660257</t>
+          <t>666943</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>660257</t>
+          <t>666943</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>660257</t>
+          <t>666943</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62018</t>
+          <t>68165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115366</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242851</t>
+          <t>67999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>160643</t>
+          <t>103371</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94250</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335024</t>
+          <t>126137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>265713</t>
+          <t>322428</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248972</t>
+          <t>303295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278739</t>
+          <t>336087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>359951</t>
+          <t>367199</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232466</t>
+          <t>353539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>428492</t>
+          <t>379306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>625664</t>
+          <t>689627</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451283</t>
+          <t>666861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692057</t>
+          <t>708763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310990</t>
+          <t>371460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310990</t>
+          <t>371460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310990</t>
+          <t>371460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475317</t>
+          <t>421538</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475317</t>
+          <t>421538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475317</t>
+          <t>421538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>786307</t>
+          <t>792998</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>786307</t>
+          <t>792998</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>786307</t>
+          <t>792998</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>42595</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>33762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>55129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36316</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>73403</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53381</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>88854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>161710</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131929</t>
+          <t>149176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149902</t>
+          <t>170543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>179542</t>
+          <t>195575</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171545</t>
+          <t>187972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186285</t>
+          <t>202630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>320845</t>
+          <t>357286</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>307926</t>
+          <t>341835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331860</t>
+          <t>369330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>177380</t>
+          <t>204305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177380</t>
+          <t>204305</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177380</t>
+          <t>204305</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207861</t>
+          <t>226383</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207861</t>
+          <t>226383</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207861</t>
+          <t>226383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385241</t>
+          <t>430689</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385241</t>
+          <t>430689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385241</t>
+          <t>430689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>27167</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>45315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>256941</t>
+          <t>256576</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248832</t>
+          <t>248901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262049</t>
+          <t>261676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>239563</t>
+          <t>244441</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232037</t>
+          <t>236583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245865</t>
+          <t>250712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>496504</t>
+          <t>501017</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>486160</t>
+          <t>488723</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504534</t>
+          <t>509172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269245</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269245</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269245</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526301</t>
+          <t>534038</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526301</t>
+          <t>534038</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526301</t>
+          <t>534038</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>108256</t>
+          <t>125548</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87426</t>
+          <t>103955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139202</t>
+          <t>152012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>312791</t>
+          <t>132349</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136015</t>
+          <t>113555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>580883</t>
+          <t>152173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>421046</t>
+          <t>257897</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>238737</t>
+          <t>227522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>795938</t>
+          <t>289751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>510432</t>
+          <t>587318</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>479486</t>
+          <t>560854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>531262</t>
+          <t>608911</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>535661</t>
+          <t>638270</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267569</t>
+          <t>618446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712437</t>
+          <t>657064</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1046093</t>
+          <t>1225587</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671201</t>
+          <t>1193733</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1228402</t>
+          <t>1255962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>618688</t>
+          <t>712866</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>618688</t>
+          <t>712866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>618688</t>
+          <t>712866</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848452</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848452</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848452</t>
+          <t>770619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1467139</t>
+          <t>1483484</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1467139</t>
+          <t>1483484</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1467139</t>
+          <t>1483484</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>408240</t>
+          <t>475516</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>182453</t>
+          <t>446821</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>564222</t>
+          <t>503416</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>405732</t>
+          <t>469070</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>382277</t>
+          <t>440625</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>427553</t>
+          <t>494294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>813972</t>
+          <t>944586</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>506725</t>
+          <t>903403</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>972250</t>
+          <t>984875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>518076</t>
+          <t>319973</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>362094</t>
+          <t>292073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>743863</t>
+          <t>348668</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>311999</t>
+          <t>362261</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>290178</t>
+          <t>337037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>335454</t>
+          <t>390706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>830076</t>
+          <t>682235</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>671798</t>
+          <t>641946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1137323</t>
+          <t>723418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926316</t>
+          <t>795489</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926316</t>
+          <t>795489</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926316</t>
+          <t>795489</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644048</t>
+          <t>1626821</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644048</t>
+          <t>1626821</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644048</t>
+          <t>1626821</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>740606</t>
+          <t>845192</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>582424</t>
+          <t>787103</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>821203</t>
+          <t>901671</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1066004</t>
+          <t>909481</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>866545</t>
+          <t>866526</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1559226</t>
+          <t>957580</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1806611</t>
+          <t>1754674</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1589899</t>
+          <t>1681482</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2362623</t>
+          <t>1829631</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2704784</t>
+          <t>2671626</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2624187</t>
+          <t>2615147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2862966</t>
+          <t>2729715</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2591059</t>
+          <t>2819434</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2097837</t>
+          <t>2771335</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2790518</t>
+          <t>2862389</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5295842</t>
+          <t>5491060</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4739830</t>
+          <t>5416103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5512554</t>
+          <t>5564252</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3445390</t>
+          <t>3516818</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657063</t>
+          <t>3728915</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7102453</t>
+          <t>7245734</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
